--- a/test_data/chassis.xlsx
+++ b/test_data/chassis.xlsx
@@ -550,7 +550,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>?????????</t>
+          <t>1 正常验证 get_agv_main_version（ID=1）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>??set_agv_led_mode?0???</t>
+          <t>1 正常验证 set_agv_led_mode（ID=1，state=0）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>??set_agv_led_mode?1???</t>
+          <t>2 正常验证 set_agv_led_mode（ID=2，state=1）</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>??set_agv_led_mode????-1</t>
+          <t>3 异常验证 set_agv_led_mode（ID=3，state=-1）</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>??set_agv_led_mode????2</t>
+          <t>4 异常验证 set_agv_led_mode（ID=4，state=2）</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>??????????</t>
+          <t>1 正常验证 is_agv_powered_on（ID=1）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>??????????</t>
+          <t>1 正常验证 get_agv_move_state（ID=1）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>???????????</t>
+          <t>1 正常验证 get_agv_robot_status（ID=1）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>?????????</t>
+          <t>1 正常验证 get_agv_encoder（ID=1）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>????????</t>
+          <t>1 正常验证 get_agv_liftmm（ID=1）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>??????????</t>
+          <t>1 正常验证 is_agv_lift_init_calibrate（ID=1）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>?????????</t>
+          <t>1 正常验证 get_agv_lift_zero_encoder（ID=1）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>????????</t>
+          <t>1 正常验证 get_agv_zero_status（ID=1）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>????????</t>
+          <t>1 正常验证 get_agv_joints_status（ID=1）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>??????????</t>
+          <t>1 正常验证 get_agv_modify_version（ID=1）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>??????????</t>
+          <t>1 正常验证 get_agv_motors_run_sp（ID=1）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>????????</t>
+          <t>1 正常验证 get_agv_motors_current（ID=1）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>????????</t>
+          <t>1 正常验证 get_agv_motors_temp（ID=1）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>??????????</t>
+          <t>1 正常验证 get_agv_motors_loss_count（ID=1）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>?????????-device_id=1</t>
+          <t>1 正常验证 get_agv_motor_acc（ID=1，device_id=1）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>?????????-device_id=2</t>
+          <t>2 正常验证 get_agv_motor_acc（ID=2，device_id=2）</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>?????????-device_id=3</t>
+          <t>3 正常验证 get_agv_motor_acc（ID=3，device_id=3）</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>????100Hz????</t>
+          <t>1 正常验证 get_agv_report_msg（ID=1）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>????20Hz????</t>
+          <t>1 正常验证 get_agv_report_msg_20hz（ID=1）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>??????????</t>
+          <t>1 正常验证 get_agv_wheel_brake（ID=1）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>??????????300</t>
+          <t>AMA001 正常验证 set_agv_motor_acc（ID=AMA001，device_id=1，acc=300）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>??????????300</t>
+          <t>AMA002 正常验证 set_agv_motor_acc（ID=AMA002，device_id=2，acc=300）</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>??????????300</t>
+          <t>AMA003 正常验证 set_agv_motor_acc（ID=AMA003，device_id=3，acc=300）</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>?????????</t>
+          <t>APO001 正常验证 agv_power_on（ID=APO001）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>??????debug??</t>
+          <t>1 正常验证 get_agv_debug_state（ID=1）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>???????????</t>
+          <t>APF001 正常验证 agv_power_off（ID=APF001）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>?????????????</t>
+          <t>ACE001 正常验证 clear_agv_error（ID=ACE001，device_id=254）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ACK??</t>
+          <t>ACK 响应</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>??????????</t>
+          <t>AWC001 正常验证 agv_wheel_control（ID=AWC001，forward_mps=0.05，rotate_rads=0，duration=1）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ACK??</t>
+          <t>ACK 响应</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>??????????</t>
+          <t>AWC002 正常验证 agv_wheel_control（ID=AWC002，forward_mps=0，rotate_rads=0.1，duration=1）</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ACK??</t>
+          <t>ACK 响应</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>?????????</t>
+          <t>AWS001 正常验证 agv_wheel_stop（ID=AWS001，forward_mps=0.05，duration=0.5）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ACK??</t>
+          <t>ACK 响应</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>???????????</t>
+          <t>AWE001 正常验证 set_agv_wheel_enabled（ID=AWE001，device_id=254，state=0）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ACK??</t>
+          <t>ACK 响应</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>?????????</t>
+          <t>AWB001 正常验证 set_agv_wheel_brake（ID=AWB001，state=0）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>?????????</t>
+          <t>AWB002 正常验证 set_agv_wheel_brake（ID=AWB002，state=1）</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>???????50?????</t>
+          <t>ALM001 正常验证 set_agv_liftmm（ID=ALM001，lift_mm=50，speed=20，tolerance=2）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>?????????????</t>
+          <t>ALC001 正常验证 set_agv_lift_calibrate（ID=ALC001）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>????????????????????????????</t>
+          <t>确认升降机构周边无人员和障碍物，可随时急停</t>
         </is>
       </c>
       <c r="E2" t="b">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LED????????????</t>
+          <t>ALD001 正常验证 set_agv_led_color（ID=ALD001，r=255，g=0，b=0，brightness=50）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ACK??</t>
+          <t>ACK 响应</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>??set_agv_debug_state?0???</t>
+          <t>1 正常验证 set_agv_debug_state（ID=1，state=0）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>??set_agv_debug_state?2???</t>
+          <t>2 正常验证 set_agv_debug_state（ID=2，state=2）</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>??set_agv_debug_state?4???</t>
+          <t>3 正常验证 set_agv_debug_state（ID=3，state=4）</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>??set_agv_debug_state????-1</t>
+          <t>4 异常验证 set_agv_debug_state（ID=4，state=-1）</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>??set_agv_debug_state????5</t>
+          <t>5 异常验证 set_agv_debug_state（ID=5，state=5）</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>????????????</t>
+          <t>1 正常验证 get_agv_auto_report（ID=1）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>??set_agv_auto_report?0???</t>
+          <t>1 正常验证 set_agv_auto_report（ID=1，state=0）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>??set_agv_auto_report?1???</t>
+          <t>2 正常验证 set_agv_auto_report（ID=2，state=1）</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>??set_agv_auto_report????-1</t>
+          <t>3 异常验证 set_agv_auto_report（ID=3，state=-1）</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>??set_agv_auto_report????2</t>
+          <t>4 异常验证 set_agv_auto_report（ID=4，state=2）</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>??????????</t>
+          <t>1 正常验证 get_agv_handle_state（ID=1）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>??set_agv_handle_state?0???</t>
+          <t>1 正常验证 set_agv_handle_state（ID=1，state=0）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>??set_agv_handle_state?1???</t>
+          <t>2 正常验证 set_agv_handle_state（ID=2，state=1）</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>??????LED??</t>
+          <t>1 正常验证 get_agv_led_mode（ID=1）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
